--- a/src/FR 509-B Suivi pièces master.xlsx
+++ b/src/FR 509-B Suivi pièces master.xlsx
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Date: 20/07/2026</v>
+        <v>Date: 21/07/2026</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -594,7 +594,7 @@
         <v>second test master</v>
       </c>
       <c r="B6" t="str">
-        <v>MASTER_454</v>
+        <v>MASTER_453</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -626,10 +626,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>second test master</v>
+        <v>test creation new master</v>
       </c>
       <c r="B7" t="str">
-        <v>MASTER_453</v>
+        <v>MASTER_455</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -647,7 +647,7 @@
         <v>20/07/2026</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>for test</v>
       </c>
       <c r="I7" t="str">
         <v>Active</v>

--- a/src/FR 509-B Suivi pièces master.xlsx
+++ b/src/FR 509-B Suivi pièces master.xlsx
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Date: 21/07/2026</v>
+        <v>Date: 22/07/2026</v>
       </c>
       <c r="B3" t="str">
         <v/>
